--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488256_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488256_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. FAJANA</t>
+          <t>M. KOZAR SIMIONIKA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6516</v>
+        <v>2.2306</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8519</v>
+        <v>2.734</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5035</v>
+        <v>-0.5034</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4299</v>
+        <v>1.4811</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5174</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.7296</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6024</v>
+        <v>2.5534</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5289</v>
+        <v>1.1635</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0735</v>
+        <v>1.3899</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1725</v>
+        <v>-1.0723</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0115</v>
+        <v>-0.412</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.161</v>
+        <v>-0.6603</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4823</v>
+        <v>1.297</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.891</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4087</v>
+        <v>1.297</v>
       </c>
       <c r="S2" t="n">
-        <v>1.389</v>
+        <v>0.3958</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1927</v>
+        <v>0.1806</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5817</v>
+        <v>0.2151</v>
       </c>
       <c r="V2" t="n">
-        <v>0.315</v>
+        <v>-0.9433</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3144</v>
+        <v>-0.9433</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. DELGADO YEBOAH</t>
+          <t>O. FAJANA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22</v>
+        <v>2.116</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8142</v>
+        <v>-0.8951</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5941</v>
+        <v>3.0111</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3324</v>
+        <v>2.4299</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3343</v>
+        <v>2.5174</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6666</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.08359999999999999</v>
+        <v>2.6024</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1677</v>
+        <v>2.5289</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0842</v>
+        <v>0.0735</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2488</v>
+        <v>-0.1725</v>
       </c>
       <c r="N3" t="n">
-        <v>0.502</v>
+        <v>-0.0115</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7508</v>
+        <v>-0.161</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9264</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1117</v>
+        <v>-3.891</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0382</v>
+        <v>2.4087</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4238</v>
+        <v>0.8534</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5484</v>
+        <v>-0.2359</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1246</v>
+        <v>1.0893</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2022</v>
+        <v>0.315</v>
       </c>
       <c r="W3" t="n">
-        <v>3.461</v>
+        <v>0.6294</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. KOZAR SIMIONIKA</t>
+          <t>K. DELGADO YEBOAH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1452</v>
+        <v>1.8404</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7225</v>
+        <v>2.336</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5773</v>
+        <v>-0.4957</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4811</v>
+        <v>-1.3324</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.3343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7296</v>
+        <v>-1.6666</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5534</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1635</v>
+        <v>-0.1677</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3899</v>
+        <v>0.0842</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0723</v>
+        <v>-1.2488</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.412</v>
+        <v>0.502</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6603</v>
+        <v>-1.7508</v>
       </c>
       <c r="P4" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R4" t="n">
-        <v>1.297</v>
+        <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3104</v>
+        <v>0.0441</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1691</v>
+        <v>0.0703</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1412</v>
+        <v>-0.0261</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9433</v>
+        <v>2.2022</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.461</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9433</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. TRUJILLO SUAREZ</t>
+          <t>J. REYES BARRANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5386</v>
+        <v>1.6911</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0721</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4665</v>
+        <v>2.5595</v>
       </c>
       <c r="G5" t="n">
-        <v>1.222</v>
+        <v>1.6402</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5153</v>
+        <v>3.7355</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7373</v>
+        <v>-2.0953</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4887</v>
+        <v>1.4908</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1201</v>
+        <v>3.4482</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3686</v>
+        <v>-1.9573</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2667</v>
+        <v>0.1493</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6354</v>
+        <v>0.2873</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3687</v>
+        <v>-0.138</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7411</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.891</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7411</v>
+        <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4245</v>
+        <v>0.0155</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4166</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.008</v>
+        <v>0.6864</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. REYES BARRANCO</t>
+          <t>S. TRUJILLO SUAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2682</v>
+        <v>1.642</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1189</v>
+        <v>1.2247</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3871</v>
+        <v>0.4172</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6402</v>
+        <v>1.222</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7355</v>
+        <v>-0.5153</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0953</v>
+        <v>1.7373</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4908</v>
+        <v>1.4887</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4482</v>
+        <v>0.1201</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9573</v>
+        <v>1.3686</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1493</v>
+        <v>-0.2667</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2873</v>
+        <v>-0.6354</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.138</v>
+        <v>0.3687</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.891</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0382</v>
+        <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4074</v>
+        <v>-0.3211</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9214</v>
+        <v>-0.2639</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5141</v>
+        <v>-0.0572</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4404</v>
+        <v>0.1051</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6402</v>
+        <v>-2.2917</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1998</v>
+        <v>2.3968</v>
       </c>
       <c r="G8" t="n">
         <v>-0.643</v>
@@ -1078,13 +1078,13 @@
         <v>1.1117</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1298</v>
+        <v>0.4156</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.5058</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7245</v>
+        <v>0.9214</v>
       </c>
       <c r="V8" t="n">
         <v>1.2589</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8879</v>
+        <v>-0.8085</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.867</v>
+        <v>-1.8123</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9792</v>
+        <v>1.0038</v>
       </c>
       <c r="G9" t="n">
         <v>0.898</v>
@@ -1156,13 +1156,13 @@
         <v>1.1117</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2141</v>
+        <v>0.2935</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.143</v>
+        <v>-0.0883</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3571</v>
+        <v>0.3818</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2589</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>V. PIETUKHOV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2957</v>
+        <v>-1.498</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6917</v>
+        <v>-1.615</v>
       </c>
       <c r="F10" t="n">
-        <v>2.396</v>
+        <v>0.1169</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8568</v>
+        <v>-1.5088</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7601</v>
+        <v>0.5188</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9033</v>
+        <v>-2.0276</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3505</v>
+        <v>-0.6742</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.5164</v>
+        <v>0.4549</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1659</v>
+        <v>-1.1292</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4937</v>
+        <v>-0.8345</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2437</v>
+        <v>0.0639</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7374000000000001</v>
+        <v>-0.8984</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2234</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9646</v>
+        <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2101</v>
+        <v>-0.2307</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6354</v>
+        <v>-0.0143</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8456</v>
+        <v>-0.2164</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5744</v>
+        <v>-0.3144</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3155</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. PIETUKHOV</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9702</v>
+        <v>-1.5419</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8655</v>
+        <v>-3.6917</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1047</v>
+        <v>2.1498</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5088</v>
+        <v>-0.8568</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5188</v>
+        <v>-1.7601</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0276</v>
+        <v>0.9033</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6742</v>
+        <v>-1.3505</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4549</v>
+        <v>-1.5164</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1292</v>
+        <v>0.1659</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8345</v>
+        <v>0.4937</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0639</v>
+        <v>-0.2437</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8984</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5558999999999999</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>-2.9646</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4823</v>
+        <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7028</v>
+        <v>-0.0361</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2649</v>
+        <v>-0.6354</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.438</v>
+        <v>0.5994</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3144</v>
+        <v>1.5744</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3144</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.195600000000001</v>
+        <v>6.743000000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4602</v>
+        <v>-3.9133</v>
       </c>
       <c r="F12" t="n">
         <v>10.656</v>
@@ -1357,10 +1357,10 @@
         <v>4.2964</v>
       </c>
       <c r="H12" t="n">
-        <v>6.485099999999998</v>
+        <v>6.485099999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1886</v>
+        <v>-2.188599999999999</v>
       </c>
       <c r="J12" t="n">
         <v>6.115399999999998</v>
@@ -1369,7 +1369,7 @@
         <v>6.7313</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6158000000000003</v>
+        <v>-0.6158000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-1.819</v>
@@ -1390,13 +1390,13 @@
         <v>12.97</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8829000000000001</v>
+        <v>1.43</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.7108</v>
+        <v>-2.1636</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5936</v>
+        <v>3.5937</v>
       </c>
       <c r="V12" t="n">
         <v>4.7222</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4227</v>
+        <v>3.1123</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9976</v>
+        <v>1.2142</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4251</v>
+        <v>1.8981</v>
       </c>
       <c r="G13" t="n">
         <v>-0.2984</v>
@@ -1468,13 +1468,13 @@
         <v>2.2234</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8687</v>
+        <v>0.5584</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6119</v>
+        <v>-0.1716</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2569</v>
+        <v>0.7299</v>
       </c>
       <c r="V13" t="n">
         <v>0.6289</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.474</v>
+        <v>0.8469</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5144</v>
+        <v>-0.2206</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9883</v>
+        <v>1.0674</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0927</v>
@@ -1546,13 +1546,13 @@
         <v>3.1499</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1189</v>
+        <v>0.254</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0769</v>
+        <v>-0.7831</v>
       </c>
       <c r="U14" t="n">
-        <v>0.958</v>
+        <v>1.0371</v>
       </c>
       <c r="V14" t="n">
         <v>0.315</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. HERNÁNDEZ CASTAÑO</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3221</v>
+        <v>0.825</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3221</v>
+        <v>-1.161</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.986</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3221</v>
+        <v>-0.2097</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3221</v>
+        <v>-0.3493</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.1396</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3221</v>
+        <v>-0.2597</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3221</v>
+        <v>0.1845</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.4443</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.5839</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.9646</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.9646</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0.3566</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.9012</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.5446</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ RAMADA</t>
+          <t>H. HERNÁNDEZ CASTAÑO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1775</v>
+        <v>0.3221</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2224</v>
+        <v>0.3221</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3999</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0305</v>
+        <v>0.3221</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2721</v>
+        <v>0.3221</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3026</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1059</v>
+        <v>0.3221</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0644</v>
+        <v>0.3221</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0415</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3366</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2611</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0383</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3283</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. PENAS REINO</t>
+          <t>D. RODRIGUEZ RAMADA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,22 +1735,22 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3202</v>
+        <v>0.3</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0501</v>
+        <v>-0.1245</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7299</v>
+        <v>0.4245</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4833</v>
+        <v>0.0305</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0574</v>
+        <v>-0.2721</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.3026</v>
       </c>
       <c r="J17" t="n">
         <v>0.1059</v>
@@ -1762,46 +1762,46 @@
         <v>0.0415</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3774</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1219</v>
+        <v>-0.3366</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4993</v>
+        <v>0.2611</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6558</v>
+        <v>0.0843</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.526</v>
+        <v>-0.2304</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1298</v>
+        <v>0.3146</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2594</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>D. PENAS REINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4984</v>
+        <v>0.2032</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8465</v>
+        <v>-0.8542</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3481</v>
+        <v>1.0575</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2097</v>
+        <v>0.4833</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3493</v>
+        <v>-0.0574</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1396</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2597</v>
+        <v>0.1059</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1845</v>
+        <v>0.0644</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4443</v>
+        <v>0.0415</v>
       </c>
       <c r="M18" t="n">
-        <v>0.05</v>
+        <v>0.3774</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.1219</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5839</v>
+        <v>0.4993</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9646</v>
+        <v>1.1117</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9646</v>
+        <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.68</v>
+        <v>-0.1324</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.5867</v>
+        <v>-0.3301</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.1977</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5733</v>
+        <v>-1.2594</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5733</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>F. VALDIVIA SANTILLANA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5496</v>
+        <v>0.0779</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0064</v>
+        <v>-1.0836</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5432</v>
+        <v>1.1615</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8734</v>
+        <v>0.9628</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0288</v>
+        <v>-0.065</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8446</v>
+        <v>1.0277</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.511</v>
+        <v>2.0497</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0655</v>
+        <v>0.5153</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4455</v>
+        <v>1.5344</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3624</v>
+        <v>-1.087</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9633</v>
+        <v>-0.5803</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3991</v>
+        <v>-0.5067</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7411</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R19" t="n">
-        <v>2.594</v>
+        <v>2.0382</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5276</v>
+        <v>0.1707</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1553</v>
+        <v>-0.3541</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3723</v>
+        <v>0.5248</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.945</v>
+        <v>-0.3144</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2022</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.1471</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. VALDIVIA SANTILLANA</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3194</v>
+        <v>-2.1032</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7691</v>
+        <v>-1.2795</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4497</v>
+        <v>-0.8237</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9628</v>
+        <v>-2.8734</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.065</v>
+        <v>-2.0288</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0277</v>
+        <v>-0.8446</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0497</v>
+        <v>-1.511</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5153</v>
+        <v>-1.0655</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5344</v>
+        <v>-0.4455</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.087</v>
+        <v>-1.3624</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5803</v>
+        <v>-0.9633</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5067</v>
+        <v>-0.3991</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7411</v>
+        <v>0.7411</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0382</v>
+        <v>2.594</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2266</v>
+        <v>0.974</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0396</v>
+        <v>-0.1178</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.187</v>
+        <v>1.0918</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3144</v>
+        <v>-0.945</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.2022</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3144</v>
+        <v>-3.1471</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0773</v>
+        <v>-2.7584</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5093</v>
+        <v>-2.3134</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5681</v>
+        <v>-0.4449</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0353</v>
@@ -2092,13 +2092,13 @@
         <v>0.1853</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3009</v>
+        <v>0.018</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.383</v>
+        <v>-0.1871</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.2052</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8269</v>
+        <v>-4.41</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0574</v>
+        <v>-5.1554</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2306</v>
+        <v>0.7454</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5857</v>
@@ -2170,13 +2170,13 @@
         <v>2.2234</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2586</v>
+        <v>0.1582</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4203</v>
+        <v>-0.5182</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1616</v>
+        <v>0.6765</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5738</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1955</v>
+        <v>-3.5842</v>
       </c>
       <c r="E23" t="n">
         <v>-10.6559</v>
       </c>
       <c r="F23" t="n">
-        <v>4.4603</v>
+        <v>7.071800000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2965</v>
@@ -2224,7 +2224,7 @@
         <v>1.8191</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2463000000000002</v>
+        <v>0.2463</v>
       </c>
       <c r="L23" t="n">
         <v>1.5726</v>
@@ -2233,13 +2233,13 @@
         <v>-6.115499999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-6.7314</v>
+        <v>-6.731399999999999</v>
       </c>
       <c r="O23" t="n">
         <v>0.6158999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>3.705799999999999</v>
+        <v>3.7058</v>
       </c>
       <c r="Q23" t="n">
         <v>-12.9701</v>
@@ -2248,13 +2248,13 @@
         <v>16.6758</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8827999999999996</v>
+        <v>1.7286</v>
       </c>
       <c r="T23" t="n">
         <v>-3.5936</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7108</v>
+        <v>5.3222</v>
       </c>
       <c r="V23" t="n">
         <v>-4.722</v>
